--- a/SGC-CKN/Excel/789986b6-4cba-4c1f-9f23-d601df4ed9f8_Thi_công_cọc_khoan_nhồi_C1-523_D1200_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/789986b6-4cba-4c1f-9f23-d601df4ed9f8_Thi_công_cọc_khoan_nhồi_C1-523_D1200_06-04-2026.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>00:00 06/04/2026</t>
+    <t>00:01 06/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -199,7 +199,7 @@
     <t>Cuội sỏi lẫn cát sạn, dám sạn, đa màu sắc, trạng thái rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">00:00
+    <t xml:space="preserve">00:01
 06/04/2026</t>
   </si>
   <si>
@@ -1542,13 +1542,13 @@
         <v>-72.9</v>
       </c>
       <c r="H20" s="35">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I20" s="35">
         <v>2.9</v>
       </c>
       <c r="J20" s="8">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="K20" s="36" t="s">
         <v>30</v>
@@ -1970,13 +1970,13 @@
         <v>-72.9</v>
       </c>
       <c r="G11" s="35">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H11" s="35">
         <v>2.9</v>
       </c>
       <c r="I11" s="8">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1999,7 +1999,7 @@
         <v>-72.9</v>
       </c>
       <c r="G12" s="40">
-        <v>35.92</v>
+        <v>35.93</v>
       </c>
       <c r="H12" s="40">
         <v>69.73</v>

--- a/SGC-CKN/Excel/789986b6-4cba-4c1f-9f23-d601df4ed9f8_Thi_công_cọc_khoan_nhồi_C1-523_D1200_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/789986b6-4cba-4c1f-9f23-d601df4ed9f8_Thi_công_cọc_khoan_nhồi_C1-523_D1200_06-04-2026.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>00:01 06/04/2026</t>
+    <t>00:00 06/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -199,7 +199,7 @@
     <t>Cuội sỏi lẫn cát sạn, dám sạn, đa màu sắc, trạng thái rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">00:01
+    <t xml:space="preserve">00:00
 06/04/2026</t>
   </si>
   <si>
@@ -1542,13 +1542,13 @@
         <v>-72.9</v>
       </c>
       <c r="H20" s="35">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="I20" s="35">
         <v>2.9</v>
       </c>
       <c r="J20" s="8">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="K20" s="36" t="s">
         <v>30</v>
@@ -1970,13 +1970,13 @@
         <v>-72.9</v>
       </c>
       <c r="G11" s="35">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H11" s="35">
         <v>2.9</v>
       </c>
       <c r="I11" s="8">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1999,7 +1999,7 @@
         <v>-72.9</v>
       </c>
       <c r="G12" s="40">
-        <v>35.93</v>
+        <v>35.92</v>
       </c>
       <c r="H12" s="40">
         <v>69.73</v>

--- a/SGC-CKN/Excel/789986b6-4cba-4c1f-9f23-d601df4ed9f8_Thi_công_cọc_khoan_nhồi_C1-523_D1200_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/789986b6-4cba-4c1f-9f23-d601df4ed9f8_Thi_công_cọc_khoan_nhồi_C1-523_D1200_06-04-2026.xlsx
@@ -190,7 +190,7 @@
   </si>
   <si>
     <t xml:space="preserve">23:05
-06/04/2026</t>
+05/04/2026</t>
   </si>
   <si>
     <t>10</t>
@@ -237,7 +237,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -313,12 +313,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF134E4A"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -336,7 +330,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -411,11 +405,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -516,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -620,22 +609,19 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1507,67 +1493,67 @@
         <v>-70</v>
       </c>
       <c r="H19" s="31">
-        <v>26.58</v>
+        <v>2.58</v>
       </c>
       <c r="I19" s="31">
         <v>8.06</v>
       </c>
-      <c r="J19" s="34">
-        <v>0.3</v>
+      <c r="J19" s="8">
+        <v>3.12</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="E20" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="34">
         <v>-70</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="34">
         <v>-72.9</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="34">
         <v>0.92</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="34">
         <v>2.9</v>
       </c>
       <c r="J20" s="8">
         <v>3.16</v>
       </c>
-      <c r="K20" s="36" t="s">
+      <c r="K20" s="35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1941,38 +1927,38 @@
         <v>-70</v>
       </c>
       <c r="G10" s="31">
-        <v>26.58</v>
+        <v>2.58</v>
       </c>
       <c r="H10" s="31">
         <v>8.06</v>
       </c>
-      <c r="I10" s="34">
-        <v>0.3</v>
+      <c r="I10" s="8">
+        <v>3.12</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="A11" s="34">
         <v>10</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="34">
         <v>1</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="34">
         <v>-70</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="34">
         <v>-72.9</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="34">
         <v>0.92</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="34">
         <v>2.9</v>
       </c>
       <c r="I11" s="8">
@@ -1980,32 +1966,32 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>10</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="39">
         <v>-3.17</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="39">
         <v>-72.9</v>
       </c>
-      <c r="G12" s="40">
-        <v>35.92</v>
-      </c>
-      <c r="H12" s="40">
+      <c r="G12" s="39">
+        <v>11.92</v>
+      </c>
+      <c r="H12" s="39">
         <v>69.73</v>
       </c>
-      <c r="I12" s="40">
-        <v>1.94</v>
+      <c r="I12" s="39">
+        <v>5.85</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/789986b6-4cba-4c1f-9f23-d601df4ed9f8_Thi_công_cọc_khoan_nhồi_C1-523_D1200_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/789986b6-4cba-4c1f-9f23-d601df4ed9f8_Thi_công_cọc_khoan_nhồi_C1-523_D1200_06-04-2026.xlsx
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>09:30 05/04/2026</t>
+    <t>11:25 05/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
@@ -200,7 +200,7 @@
   </si>
   <si>
     <t xml:space="preserve">00:00
-06/04/2026</t>
+05/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
